--- a/mortality_SPPA_2way_interpolation.xlsx
+++ b/mortality_SPPA_2way_interpolation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Eric\git\ICM_LAVegMod\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B679324A-052C-4EC2-9EB2-02AED2005EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C505572E-EF1F-4B76-AB1E-5BA34105893E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{74F289D0-3EE8-459D-9BEF-E30A003D3322}"/>
   </bookViews>
@@ -1627,7 +1627,7 @@
         <v>2</v>
       </c>
       <c r="AB4" s="17">
-        <v>2.3199999999999998</v>
+        <v>1.5</v>
       </c>
       <c r="AC4" s="20" t="s">
         <v>15</v>
@@ -1890,11 +1890,11 @@
       </c>
       <c r="AB7" s="8">
         <f ca="1">OFFSET($A$1,_xlfn.XMATCH(Y,$A$2:$A$40,1),0)</f>
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AC7" s="24">
         <f ca="1">MATCH(AB7,$A$2:$A$40)</f>
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -1978,11 +1978,11 @@
       </c>
       <c r="AB8" s="9">
         <f ca="1">OFFSET($A$1,_xlfn.XMATCH(Y,$A$2:$A$40,-1),0)</f>
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AC8" s="25">
         <f ca="1">MATCH(AB8,$A$2:$A$40)</f>
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.25">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="AB9" s="7">
         <f ca="1">OFFSET($A$1,AC8,AC5)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AC9" s="26"/>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB10" s="8">
         <f ca="1">OFFSET($A$1,AC8,AC6)</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="AB11" s="8">
         <f ca="1">OFFSET($A$1,AC7,AC5)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.25">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="AB12" s="9">
         <f ca="1">OFFSET($A$1,AC7,AC6)</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="AB13" s="10">
         <f ca="1">VLA+(VRA-VLA)*((X-L)/(R_-L))</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14" spans="1:29" x14ac:dyDescent="0.25">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB14" s="11">
         <f ca="1">VLB+(VRB-VLB)*((X-L)/(R_-L))</f>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.25">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AB15" s="15">
         <f ca="1">VXA+(VXB-VXA)*((Y-A)/(B-A))</f>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.25">
